--- a/artfynd/A 20560-2022 artfynd.xlsx
+++ b/artfynd/A 20560-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20560-2022 artfynd.xlsx
+++ b/artfynd/A 20560-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82366155</v>
+        <v>82366107</v>
       </c>
       <c r="B2" t="n">
-        <v>95511</v>
+        <v>103250</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>221725</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>82366107</v>
+        <v>82366154</v>
       </c>
       <c r="B3" t="n">
-        <v>103250</v>
+        <v>95519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -927,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>82366154</v>
+        <v>82366136</v>
       </c>
       <c r="B4" t="n">
-        <v>95519</v>
+        <v>98431</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,16 +943,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1053,10 +1053,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>82366136</v>
+        <v>82366108</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
+        <v>101680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,16 +1069,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1172,132 +1172,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
-        <is>
-          <t>Hälsinglands flora (2019)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>82366108</v>
-      </c>
-      <c r="B6" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Daphne mezereum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Strömåsen sluttning mot Svågan, Hls</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>566333.8738459519</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6880488.393369962</v>
-      </c>
-      <c r="S6" t="n">
-        <v>100</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>ALA198908040800</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>1989-08-04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>1989-08-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Liten bäckravin, lövskog</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Björn Wannberg</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Arnold Larsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
         <is>
           <t>Hälsinglands flora (2019)</t>
         </is>
